--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="579">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -952,7 +952,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -979,7 +979,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU7/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU8/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
@@ -1028,6 +1028,60 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: The name of the test that was performed.</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Observation.subject</t>
   </si>
   <si>
@@ -1180,7 +1234,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
@@ -2100,20 +2154,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP68"/>
+  <dimension ref="A1:AP72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="140.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2122,28 +2176,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="176.73046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.58203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.9921875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="239.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.87890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6137,35 +6191,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>107</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6213,7 +6263,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>109</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6225,22 +6275,22 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>21</v>
@@ -6248,14 +6298,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6271,19 +6321,19 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>335</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>114</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
+        <v>115</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>338</v>
+        <v>116</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6321,19 +6371,19 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>120</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6345,7 +6395,7 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
@@ -6354,13 +6404,13 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>339</v>
+        <v>110</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>21</v>
@@ -6368,24 +6418,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -6394,19 +6444,19 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>146</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6455,13 +6505,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6470,19 +6520,19 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>21</v>
@@ -6490,24 +6540,24 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -6516,19 +6566,19 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>353</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6577,7 +6627,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6586,25 +6636,25 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>21</v>
@@ -6612,10 +6662,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6623,13 +6673,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6638,18 +6688,20 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>128</v>
+        <v>343</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6697,7 +6749,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6712,19 +6764,19 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>21</v>
@@ -6732,10 +6784,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6758,18 +6810,18 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6817,7 +6869,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6832,19 +6884,19 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>21</v>
@@ -6852,14 +6904,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6878,19 +6930,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6939,7 +6991,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6948,44 +7000,44 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>387</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>92</v>
@@ -6997,22 +7049,22 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -7037,13 +7089,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -7061,7 +7113,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7070,25 +7122,25 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>377</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>244</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>21</v>
@@ -7096,46 +7148,44 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>294</v>
+        <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -7159,13 +7209,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7183,13 +7233,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -7201,27 +7251,27 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7235,28 +7285,26 @@
         <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7305,7 +7353,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7320,19 +7368,19 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>21</v>
@@ -7340,10 +7388,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7357,27 +7405,29 @@
         <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7401,13 +7451,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>425</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7425,7 +7475,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7434,36 +7484,36 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>430</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7477,7 +7527,7 @@
         <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7489,16 +7539,16 @@
         <v>294</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7523,13 +7573,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7547,7 +7597,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7556,7 +7606,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7568,10 +7618,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>438</v>
+        <v>244</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7582,21 +7632,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>93</v>
@@ -7608,18 +7658,20 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>441</v>
+        <v>294</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7643,13 +7695,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7667,13 +7719,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7685,27 +7737,27 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>448</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7716,7 +7768,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7728,18 +7780,20 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7787,13 +7841,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7805,27 +7859,27 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>457</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7836,10 +7890,10 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7848,20 +7902,18 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7885,13 +7937,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7909,45 +7961,45 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>465</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7970,16 +8022,20 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -8003,13 +8059,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -8027,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>109</v>
+        <v>449</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8039,7 +8095,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -8048,10 +8104,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>110</v>
+        <v>457</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -8062,24 +8118,24 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -8088,16 +8144,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>113</v>
+        <v>459</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>114</v>
+        <v>460</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>115</v>
+        <v>461</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>116</v>
+        <v>462</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8147,81 +8203,79 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>120</v>
+        <v>458</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>21</v>
+        <v>463</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>110</v>
+        <v>465</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>113</v>
+        <v>468</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8269,45 +8323,45 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8318,10 +8372,10 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -8330,16 +8384,20 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8387,19 +8445,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>483</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8408,10 +8466,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8422,10 +8480,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8448,13 +8506,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>476</v>
+        <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>483</v>
+        <v>107</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>484</v>
+        <v>108</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8505,7 +8563,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>482</v>
+        <v>109</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8514,10 +8572,10 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8526,10 +8584,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>485</v>
+        <v>110</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8540,21 +8598,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8566,20 +8624,18 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>487</v>
+        <v>114</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>488</v>
+        <v>115</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8603,13 +8659,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>492</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8627,31 +8683,31 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>486</v>
+        <v>120</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>110</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>21</v>
@@ -8662,14 +8718,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8682,25 +8738,25 @@
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>498</v>
+        <v>116</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>499</v>
+        <v>251</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8725,13 +8781,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>501</v>
+        <v>21</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8749,7 +8805,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8761,19 +8817,19 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>244</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8784,10 +8840,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8810,18 +8866,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>506</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8869,7 +8923,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8878,7 +8932,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -8890,10 +8944,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>21</v>
+        <v>498</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8904,10 +8958,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8930,13 +8984,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>106</v>
+        <v>494</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8987,7 +9041,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8996,7 +9050,7 @@
         <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>104</v>
@@ -9008,10 +9062,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9022,10 +9076,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9036,7 +9090,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9045,21 +9099,23 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>513</v>
+        <v>294</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9083,13 +9139,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>21</v>
+        <v>509</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>21</v>
+        <v>510</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -9107,13 +9163,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9125,13 +9181,13 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>518</v>
+        <v>429</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9142,10 +9198,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9165,21 +9221,23 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>520</v>
+        <v>294</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9203,13 +9261,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9227,7 +9285,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9245,13 +9303,13 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>524</v>
+        <v>429</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9262,10 +9320,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9276,7 +9334,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9285,22 +9343,20 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>521</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9349,13 +9405,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -9370,10 +9426,10 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>530</v>
+        <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9384,10 +9440,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9413,10 +9469,10 @@
         <v>106</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>107</v>
+        <v>527</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>108</v>
+        <v>528</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9467,7 +9523,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>109</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9479,7 +9535,7 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9488,10 +9544,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>21</v>
+        <v>498</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>110</v>
+        <v>529</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9502,14 +9558,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9525,19 +9581,19 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>113</v>
+        <v>531</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>114</v>
+        <v>532</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>115</v>
+        <v>533</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>116</v>
+        <v>534</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9587,7 +9643,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>120</v>
+        <v>530</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9599,7 +9655,7 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9608,10 +9664,10 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>535</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>110</v>
+        <v>536</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9622,14 +9678,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9642,26 +9698,24 @@
         <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>113</v>
+        <v>538</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>539</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>540</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9709,7 +9763,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9721,7 +9775,7 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9730,10 +9784,10 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>535</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>244</v>
+        <v>542</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9744,10 +9798,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9755,10 +9809,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9770,19 +9824,19 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>294</v>
+        <v>477</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>315</v>
+        <v>547</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9807,13 +9861,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>539</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>540</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9831,13 +9885,13 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
@@ -9849,16 +9903,16 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>320</v>
+        <v>548</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>321</v>
+        <v>549</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>21</v>
@@ -9866,10 +9920,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9889,23 +9943,19 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>543</v>
+        <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>544</v>
+        <v>107</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9953,7 +10003,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>542</v>
+        <v>109</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9965,44 +10015,44 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>547</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -10014,20 +10064,18 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>549</v>
+        <v>114</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>550</v>
+        <v>115</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10051,13 +10099,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10075,19 +10123,19 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>548</v>
+        <v>120</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>552</v>
+        <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -10096,10 +10144,10 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -10110,14 +10158,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>402</v>
+        <v>489</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10130,25 +10178,25 @@
         <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>554</v>
+        <v>490</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>404</v>
+        <v>491</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>555</v>
+        <v>116</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>406</v>
+        <v>251</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -10173,13 +10221,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -10197,7 +10245,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>492</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10209,33 +10257,33 @@
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>411</v>
+        <v>244</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10243,10 +10291,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10255,22 +10303,22 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>463</v>
+        <v>315</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10295,13 +10343,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>21</v>
+        <v>557</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>21</v>
+        <v>558</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -10319,13 +10367,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10337,23 +10385,511 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>21</v>
+        <v>559</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>466</v>
+        <v>320</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>467</v>
+        <v>321</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AP68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP68">
+  <autoFilter ref="A1:AP72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10363,7 +10899,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-10T12:52:28-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:52:28-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T21:50:44-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:50:44-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="580">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-18T15:36:33-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,7 +452,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -680,7 +680,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -949,7 +949,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -979,7 +979,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU8/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+    <t>Note that other codes are permitted in other slices, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU9/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
@@ -1085,7 +1085,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|http://hl7.org/fhir/us/core/StructureDefinition/us-core-device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
 </t>
   </si>
   <si>
@@ -1116,7 +1116,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-us-core-3:SHALL use UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use Snomed CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
+us-core-3:The system SHALL be UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use SNOMED CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1317,7 +1317,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1405,7 +1405,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1438,7 +1438,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1478,7 +1478,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1527,7 +1527,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:SHALL use UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:The system SHALL be UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1562,7 +1562,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1612,7 +1612,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1645,7 +1645,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1682,7 +1682,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1704,7 +1704,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1765,7 +1765,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1818,6 +1818,9 @@
   </si>
   <si>
     <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2179,7 +2182,7 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.99609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
@@ -10713,7 +10716,7 @@
         <v>574</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>426</v>
+        <v>575</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10766,10 +10769,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10795,13 +10798,13 @@
         <v>82</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>481</v>
@@ -10853,7 +10856,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:36:33-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
+++ b/build/output/StructureDefinition-cibmtr-observation-lab.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="580">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -452,7 +452,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -680,7 +680,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -949,7 +949,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -979,7 +979,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU8/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+    <t>Note that other codes are permitted in other slices, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU9/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
@@ -1085,7 +1085,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|http://hl7.org/fhir/us/core/StructureDefinition/us-core-device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
 </t>
   </si>
   <si>
@@ -1116,7 +1116,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-us-core-3:SHALL use UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use Snomed CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
+us-core-3:The system SHALL be UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use SNOMED CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1317,7 +1317,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1405,7 +1405,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1438,7 +1438,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1478,7 +1478,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1527,7 +1527,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:SHALL use UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:The system SHALL be UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1562,7 +1562,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1612,7 +1612,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1645,7 +1645,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1682,7 +1682,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1704,7 +1704,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1765,7 +1765,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1818,6 +1818,9 @@
   </si>
   <si>
     <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2083,9 +2086,7 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -2181,7 +2182,7 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.99609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
@@ -10715,7 +10716,7 @@
         <v>574</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>426</v>
+        <v>575</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10768,10 +10769,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10797,13 +10798,13 @@
         <v>82</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>481</v>
@@ -10855,7 +10856,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
